--- a/backtest_runs/20260410_193731/by_symbol/SINDM/SINDM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SINDM/SINDM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-416.6399999999911</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>106353.76</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>106353.76</v>
@@ -771,7 +771,7 @@
         <v>-6405.839999999984</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>99947.92000000003</v>
@@ -909,7 +909,7 @@
         <v>-3124.800000000007</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>100208.32</v>
@@ -955,7 +955,7 @@
         <v>-104.1599999999978</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>100104.16</v>
@@ -1001,7 +1001,7 @@
         <v>-104.1599999999978</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>100000</v>
@@ -1185,7 +1185,7 @@
         <v>-156.2400000000059</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>104062.24</v>
@@ -1231,7 +1231,7 @@
         <v>-8176.560000000001</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>95885.68000000002</v>
@@ -1277,7 +1277,7 @@
         <v>-1510.319999999996</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>94375.36000000003</v>
@@ -1415,7 +1415,7 @@
         <v>-2499.840000000002</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>98229.28000000001</v>
@@ -1507,7 +1507,7 @@
         <v>-3749.759999999994</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>98020.96000000002</v>
@@ -1645,7 +1645,7 @@
         <v>-2864.400000000004</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>95156.56000000001</v>
